--- a/customer_service_forms/015_updated_nail_strip_order_form_with_quantity--customer_service_forms.xlsx
+++ b/customer_service_forms/015_updated_nail_strip_order_form_with_quantity--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>strip_type_1</t>
+          <t>strip type 1</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>strip_type_2</t>
+          <t>strip type 2</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>strip_type_3</t>
+          <t>strip type 3</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>strip_type_4</t>
+          <t>strip type 4</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>strip_type_5</t>
+          <t>strip type 5</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>strip_type_6</t>
+          <t>strip type 6</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>strip_type_7</t>
+          <t>strip type 7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>strip_type_8</t>
+          <t>strip type 8</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>size_1</t>
+          <t>size 1</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>size_2</t>
+          <t>size 2</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>size_3</t>
+          <t>size 3</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>size_4</t>
+          <t>size 4</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>color_1</t>
+          <t>color 1</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>color_2</t>
+          <t>color 2</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>color_3</t>
+          <t>color 3</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>color_4</t>
+          <t>color 4</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>color_5</t>
+          <t>color 5</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>color_6</t>
+          <t>color 6</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>color_7</t>
+          <t>color 7</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>color_8</t>
+          <t>color 8</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>color_9</t>
+          <t>color 9</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>color_10</t>
+          <t>color 10</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>color_11</t>
+          <t>color 11</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>color_12</t>
+          <t>color 12</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>color_13</t>
+          <t>color 13</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>color_14</t>
+          <t>color 14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>color_15</t>
+          <t>color 15</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>color_16</t>
+          <t>color 16</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>color_17</t>
+          <t>color 17</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>color_18</t>
+          <t>color 18</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>color_19</t>
+          <t>color 19</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>color_20</t>
+          <t>color 20</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>color_21</t>
+          <t>color 21</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>color_22</t>
+          <t>color 22</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>color_23</t>
+          <t>color 23</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>color_24</t>
+          <t>color 24</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>color_25</t>
+          <t>color 25</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>color_26</t>
+          <t>color 26</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>color_27</t>
+          <t>color 27</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>color_28</t>
+          <t>color 28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>color_29</t>
+          <t>color 29</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>color_30</t>
+          <t>color 30</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>color_31</t>
+          <t>color 31</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>color_32</t>
+          <t>color 32</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>color_33</t>
+          <t>color 33</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>color_34</t>
+          <t>color 34</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>color_35</t>
+          <t>color 35</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>color_36</t>
+          <t>color 36</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>color_37</t>
+          <t>color 37</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>color_38</t>
+          <t>color 38</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>color_39</t>
+          <t>color 39</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>color_40</t>
+          <t>color 40</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>color_41</t>
+          <t>color 41</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>color_42</t>
+          <t>color 42</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>color_43</t>
+          <t>color 43</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>color_44</t>
+          <t>color 44</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>color_45</t>
+          <t>color 45</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>color_46</t>
+          <t>color 46</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>color_47</t>
+          <t>color 47</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>color_48</t>
+          <t>color 48</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>color_49</t>
+          <t>color 49</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>color_50</t>
+          <t>color 50</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>color_51</t>
+          <t>color 51</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>color_52</t>
+          <t>color 52</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>color_53</t>
+          <t>color 53</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>color_54</t>
+          <t>color 54</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>color_55</t>
+          <t>color 55</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>color_56</t>
+          <t>color 56</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>color_57</t>
+          <t>color 57</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>color_58</t>
+          <t>color 58</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>color_59</t>
+          <t>color 59</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>color_60</t>
+          <t>color 60</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>color_61</t>
+          <t>color 61</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>color_62</t>
+          <t>color 62</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>color_63</t>
+          <t>color 63</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>color_64</t>
+          <t>color 64</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>color_65</t>
+          <t>color 65</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>color_66</t>
+          <t>color 66</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>color_67</t>
+          <t>color 67</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>color_68</t>
+          <t>color 68</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>color_69</t>
+          <t>color 69</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>color_70</t>
+          <t>color 70</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>color_71</t>
+          <t>color 71</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>color_72</t>
+          <t>color 72</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>color_73</t>
+          <t>color 73</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>color_74</t>
+          <t>color 74</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>color_75</t>
+          <t>color 75</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>color_76</t>
+          <t>color 76</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>color_77</t>
+          <t>color 77</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>color_78</t>
+          <t>color 78</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>color_79</t>
+          <t>color 79</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>color_80</t>
+          <t>color 80</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>color_81</t>
+          <t>color 81</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>color_82</t>
+          <t>color 82</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>color_83</t>
+          <t>color 83</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>color_84</t>
+          <t>color 84</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>color_85</t>
+          <t>color 85</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>color_86</t>
+          <t>color 86</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>color_87</t>
+          <t>color 87</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>color_88</t>
+          <t>color 88</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>color_89</t>
+          <t>color 89</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>color_90</t>
+          <t>color 90</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>color_91</t>
+          <t>color 91</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>color_92</t>
+          <t>color 92</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>color_93</t>
+          <t>color 93</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>color_94</t>
+          <t>color 94</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>color_95</t>
+          <t>color 95</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>color_96</t>
+          <t>color 96</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>color_97</t>
+          <t>color 97</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>color_98</t>
+          <t>color 98</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>color_99</t>
+          <t>color 99</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>color_100</t>
+          <t>color 100</t>
         </is>
       </c>
     </row>
